--- a/eval/app_full.xlsx
+++ b/eval/app_full.xlsx
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>SQL相似度: 92.53%</t>
+          <t>SQL相似度: 91.6%</t>
         </is>
       </c>
     </row>
@@ -497,11 +497,11 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9774893106278548</v>
+        <v>0.9676947136123647</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `诉求区域` = '虹口区' AND `三级分类` = '城市管理' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉事件数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `诉求区域` LIKE '%虹口区%' AND `三级分类` LIKE '%城市管理%' AND `工单类型` LIKE '%投诉举报类%';</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -532,11 +532,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9800245774361225</v>
+        <v>0.9799299066445002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `诉求区域` = '浦东新区' AND `新二级分类` = '金融' AND `工单类型` = '咨询类';</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `诉求区域` LIKE '%浦东新区%' AND `新二级分类` = '金融' AND `工单类型` = '咨询类';</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -594,11 +594,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.9861436088016327</v>
+        <v>0.9805742718588658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SELECT `诉求区域`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `四级分类` = '网上购物' AND `工单类型` = '投诉举报类' GROUP BY `诉求区域` ORDER BY `数量` DESC LIMIT 10;</t>
+          <t>SELECT `诉求区域`, COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `四级分类` = '网上购物' AND `工单类型` = '投诉举报类' GROUP BY `诉求区域` ORDER BY `投诉数量` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -615,24 +615,10 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INCORRECT</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t>市民来电反映:要求挪车。 6
-市民来电咨询:要求挪车。 4
-市民来电咨询:咨询如何挪车 4
-市民留言要求挪车。 4
-市民来电反映:要求挪车 3
-市民来电反映:要求联系车主挪车。 3
-市民来电反映:咨询如何挪车 3
-市民来电反映:“一键挪车”不成功。 2
-市民来电咨询:需要挪车。 2
-市民来电反映:其想要申请挪车。 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>本市 138
 浦东新区 14
@@ -646,12 +632,26 @@
 崇明区 2</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>本市 138
+浦东新区 14
+闵行区 6
+宝山区 5
+青浦区 5
+松江区 3
+嘉定区 3
+黄浦区 2
+本市S20高速 2
+崇明区 2</t>
+        </is>
+      </c>
       <c r="E6" t="n">
-        <v>0.9433274169287084</v>
+        <v>0.9661951174577417</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SELECT `内容描述`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `四级分类` = '排堵保畅' GROUP BY `内容描述` ORDER BY `数量` DESC LIMIT 10;</t>
+          <t>SELECT `诉求地址` AS '路段', COUNT(*) AS '上报次数' FROM `shanghai_ad_time` WHERE `四级分类` = '排堵保畅' GROUP BY `诉求地址` ORDER BY `上报次数` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -673,31 +673,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>市民反映：12345人工坐席一直忙线中，无法接入。诉求：希望管理部门及时改善。 您的投诉已根据热线管理办法核实处理，感谢您的理解和支持
-市民反映：1月8日凌晨其住在北京市朝阳区甘露园附近的酒店房间，房间内一股嘲味，非常恶心，浴池都是脏的，没办法住。虽然办理入住，但是其只呆了5分钟，酒店不肯退钱。诉求：希望管理部门督促酒店退款。 根据《上海市“12345”市民服务热线办理试行办法》相关规定，您反映的事项涉及其他外省市问题的，不属于市民服务热线的受理范围，建议向问题发生地政府提出，专此简复
-市民补充信息：商家不愿意退钱，说包装坏了，让其补60元。市民可提供图片。商家地址福建省泉州市安溪县城厢镇大寨小区65号。【最近派发的工单编号：20240120007720，工单内容：市民反映：其在拼多多平台购买金骏眉茶叶，送过来里面的包装特别脏（详见附件），礼盒包装摸上去也不舒服，感觉都是灰，市民表示是送人的，遂把茶叶退回商家，商家却不肯退钱，其表示写明退货包运费，拼多多帮着商家说话，说该商品不支持退款，商品退回去了，商家不退钱，诉求：请管理部门协调尽快退款。】 我处会将您补充的信息及时转送，请您耐心等待，专此简复
-市民反映：中通快递单号78728441135025，快递被快递员私自退回，其投诉到邮政管理局，中通快递总部，电话02131080735，工号6518，有回电沟通，但是其拨打02131080735，却拒绝接通，02131080735回拨市民，市民却无法接通。诉求：投诉中通快递故意阻碍消费者与企业的沟通。 确认
-市民反映：其乘坐海航旗下金鹏航空海口美兰到上海浦东的Y87512航班，原定计划2月20日21:30起飞，但是航班延误，航司除了拖延时间，工作人员在现场解释已调度济南的飞机，但是本身其前序航班就已因天气原因备降济南，也就是他所说的所谓调度济南的飞机完全就是废话。从21:30延误至23:20，最后又延误，提供大巴前往住宿酒店，入住时约定于2月21日3:30集合出发前往机场，后又表示取消集合等待通知，后又接到通知4:30集合前往机场，目前对于飞机何时到达，何时能够起飞没有任何解释。诉求：1.提供2月20日21:30延误之后的工作记录，解释为何除了消遣乘客外毫无任何航班安排的工作内容，在航班延误后干了些啥。2.给予正确的可信的飞机到达时间以及可飞往上海的时间。3.延误导致的误工、精力损失赔偿方案。（市民要求信息保密，需要回复） 您反映的问题可以向民航局投诉，非我处受理范围。民航局消费者事务中心有专门的电话负责受理消费者投诉，您可以拨打民航服务质量监督电话12326，该电话的工作时间为：8:00-12:00、13:00-17:00，非工作时间，您可登录中国民用航空局消费者事务中心网址：www.12326.cn ，点击“投诉”进行在线投诉
-市民反映：上述地址工地生活区养狗不栓绳子，差点咬到其（详见附件）。诉求：请管理部门督促栓好绳子。 根据《上海市“12345”市民服务热线办理试行办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及外省市问题的，我处不予受理，建议市民向问题发生地政府反映，专此简复
-市民反映：关于51期间收取高速费投诉（详见附件）。诉求：投诉五一高速收费。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，除江苏。浙江、安徽三省政务服务和“一网通办“业务事宜外，涉及其他外省市问题的建议向问题发生地政府提出，专此简复
-【投诉】市民来电反映:市民曾在12345微信小程序反映关于抖音平台主播违规问题，12345热线均没有给予电话回复告知处理结果就擅自关闭了其的工单，市民对此非常不满，要求投诉热线虚假回复。相关联的工单编号：20240603006806、20240603006976。诉求：请管理部门尽快核实给予合理解释。 已按照投诉处理流程进行核实处理
-市民反映：美团餐损扣钱，不经过骑手直接扣钱。要求提供照片不提供也不说为什么。诉求：要求处理。 涉及外省市问题，请联系当地管理部门处理，涉及企业合同纠纷，请联系企业或通过司法途径处理
-市民反映：教育局规定6月28日放暑假，富川中学八年级还要继续收费补课，当地教育局默认允许这种情况不管。诉求：投诉补课事宜。（市民要求信息保密，需要回复） 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及其他外省市问题，建议向问题发生地政府提出，专此简复
-市民反映：哈啰每天拨打电话骗贷款，早晨打，晚上打。诉求：投诉哈啰拨打骚扰电话。（市民要求信息保密，需要回复） 如果用户接到骚扰短信或者骚扰电话，可向12321网络不良与垃圾信息举报受理中心投诉举报，投诉途径：电话010-12321，微信公众号“12321受理中心”。网址：www.12321.cn以上信息由【市通信管理局】提供，信息供参考
-市民反映：【商家地址/名称:世纪华联生活超市(永隆路店) 江苏省南通市海门区海永镇永隆路16号,时间:2024/07/14 17:32:00】其2024年7月14日在上述地址世纪华联生活超市(永隆路店)购得顶美品牌削皮刀，该商品为食品接触级但是并未标注生产日期保质期；另购得红松鼠品牌童袜，该商品条码已与2019年8月21日注销，以上商品均违反相关法律法规。诉求：希望管理部门依法查处。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项涉及其他外省市问题的，不属于市民服务热线的受理范围，建议向问题发生地政府提出，专此简复
-市民反映：派单不合理，取消被罚钱，找客服反馈，客服告诉无法反馈，找不到相应通道反馈。诉求：投诉饿了么派单不合理。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及企业内部管理问题的，建议您向企业反映，专此简复
-市民反映：其没有在善林金融借过款，没有任何通知，任何短信，任何征兆就把其微信零钱，工资银行卡冻结了，其打电话过去，是一个021—6270—4567的第七清收小队接的电话，非要说其2017年借了一千块，至今未还，叫其去打银行流水证明，其问哪家银行的流水，借款合同，还有收款的账号，一问三不知，就叫其还款，问题是我没借过，为什么要还，如果证据确凿，请拿出证据，该还的我一分不少的还，没有证据请解冻我名下支付工具，工作人员态度也恶劣，而且其是成都的，上海有异地管辖权吗，异地就冻结。诉求：解冻支付工具。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，应进入，已经进入诉讼程序的或法院已判决的事项不予受理，专此简复
-市民反映：其是拼多多的一个卖家，主营美容仪。 企业与平台之间的纠纷属于企业间商事合同纠纷，热线不予受理，建议通过司法途径渠道进行维权
-市民反映：三亚保利栖麓13地块安居房存在质量问题。诉求：投诉质量问题。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及外省市问题的，建议您向问题发生地政府提出，专此简复
-市民来电反映：外省市的龙华第二外国语学校12月以来，学生好几次排练到半夜12点多，周一全天彩排，周二全天表演，
-晚上加班到9:30活动，全场十几个老师和几个学生被留下，要等到11点，小学生的身体和精神都撑不住，还不让走。然后硬坐在板凳上3，4个小时。诉求：希望相关部门能出面协调。 属地化原则，当场解答，故归档。
-市民反映：苏州新鹏物业，物业管理员服务态度差。诉求：投诉物业态度差。 根据《上海市“12345”市民服务热线办理试行办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及外省市问题，不予受理，建议向问题发生地政府提出，专此简复
-市民反映：其2021年6月18日，在淘宝商家井鼎的日淘店铺，买的两盒樟脑丸。这两盒樟脑丸是仿安速品牌的外包装，让人误以为是正品。实际包装上的名称不同，里面商品内容与正品安速也不同。上传了对照图，左边是正品，右边是假货。且商家故意不在标题“安速”，知假售价。假货的成分也无从查证，不知道是否对人的健康有影响。诉求：希望管理部门协助退款，严查此商家的所有商品。（市民要求信息保密，需要回复） 根据《上海市“12345”市民服务热线办理试行办法》相关规定，您反映的事项涉及其他外省市问题的，不属于市民服务热线的受理范围，建议向问题发生地政府提出，专此简复
-市民反映：其2021年4月购买一辆凯迪拉克XT4汽车。2024年10月3日到安徽省阜阳市进行国庆年费汽车检查，维修工人告知汽车喇叭是坏的（声音非常小），市民以前没有开过凯迪拉克汽车，一直认为声音就是这么大，维修工人把旁边的喇叭按响，做了对比，才知道从购买至今，用的喇叭都是坏的。其间多次到上汽凯迪拉克售后安徽合肥点、阜阳点、亳州点进行保养维修，上汽凯迪拉克售后工作人员没有一人告知喇叭声音小，是坏的，以至于其在三年半的时间里，使用的坏喇叭。通过400电话找到上汽凯迪拉克售后，说市民超保了，不予处理此事，态度非常差。上汽凯迪拉克售后工作人员不负责任。上汽凯迪拉克公司将责任推卸到消费者身上，诉求：要求免费更换新喇叭，并赔礼道歉。 外地修理车辆，缺少零配件，需要上海总部发出，导致车辆无法修理，建议当地维修店与上海总部沟通处理
-市民反映：其想要投诉抖音，订单：1069543774563867224，下单无法使用，自动退款，未退还其优惠券。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及餐饮券、演唱会门票券、旅游门票券、酒店券等团购券无法使用、退款、和商家存在消费纠纷问题，建议您向四川省成都市市场监管部门反映，专此简复
-市民反映：甘肃省张掖市民乐县一中西校区门口商店违规向中学生售卖烟草，一根一根的卖，伤害青少年身心健康。（市民要求信息保密，需要回复） 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，除江苏、浙江、安徽三省政务服务和“一网通办”业务事宜外，涉及其他外省市问题的，建议向问题发生地政府提出，专此简复
-市民反映：刘银华、王仰苍利用职权影响力徇私、栽赃陷害、敲诈勒索市民钱财，挪用国家赔偿，金额高达上千万，还要害死市民爷爷父亲。诉求：请查处违纪行为。 公安部举报中心在公安部、省（市）级公安机关设立12389专用举报电话，负责接收处理电话举报投诉事项。公安部督察局负责全国12389专用举报电话系统运行和接收办理工作的业务指导、分析评估和考核通报。12389主要受理反映公安机关和民警违法违纪行为、违反队伍内部管理规定等举报投诉事项。向上海市公安局反映问题的人工接听时间：周一至周五9:00-11:30；13:30-17:00（双休日和国定假日除外）以上信息由【市公安局】提供，信息供参考
-市民反映：其是入驻饿了么公司的商户，饿了么平台骑手把餐拿走超时不送餐，导致订单取消，餐品骑手吃，平台不赔偿，说这是平台规定。诉求：投诉饿了么公司。 根据《“12345”市民服务热线工作管理办法》相关规定，您反映的事项不属于市民服务热线的受理范围，涉及合同争议经济纠纷，建议通过诉讼途径处理，专此简复</t>
+          <t>20240108002002 2025-01-08 08:39:11
+20240108007662 2025-01-08 10:22:49
+20240120015302 2025-01-20 16:27:26
+20240126029422 2025-01-26 20:21:59
+20240221001242 2025-02-21 08:12:14
+20240414008702 2025-04-14 12:07:47
+20240503002872 2025-05-03 09:26:39
+20240606010952 2025-06-06 11:04:58
+20240618002312 2025-06-18 08:26:33
+20240628020622 2025-06-28 14:11:53
+20240706023462 2025-07-06 18:01:36
+20240714025332 2025-07-14 21:24:19
+20240728001362 2025-07-28 08:15:10
+20240811014792 2025-08-11 15:06:38
+20240817020082 2025-08-17 16:27:11
+20240918019322 2025-09-18 12:31:57
+20231215019952 2024-12-15 14:52:31
+20231223012662 2024-12-23 14:06:07
+20231227016912 2024-12-27 13:34:07
+20241012015252 2025-10-12 11:45:36
+20241023021492 2025-10-23 14:00:33
+20241030004852 2025-10-30 09:28:52
+20241121002022 2025-11-21 08:30:01
+20241201016122 2025-12-01 14:37:46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -711,11 +710,11 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.8961755987935562</v>
+        <v>0.8782280774376676</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SELECT `内容描述`, `处理描述`, `客户类型`, `工单生成时间` FROM `shanghai_ad_time` WHERE `工单类型` = '投诉举报类' AND `诉求区域` = '其他';</t>
+          <t>SELECT `工单编号`, `工单生成时间`, `诉求地址`, `内容描述`, `工单类别`, `处理描述`, `客户类型`, `一级分类`, `二级分类`, `三级分类`, `四级分类`, `主办单位`, `是否匿名`, `服务类型`, `通话编号`, `工单类型`, `新一级分类`, `新二级分类`, `新三级分类`, `新四级分类`, `新五级分类` FROM `shanghai_ad_time` WHERE `诉求区域` LIKE '%其他%' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -737,7 +736,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0 None</t>
+          <t>127 嘉定区,奉贤区,宝山区,崇明区,徐汇区,普陀区,本市,杨浦区,松江区,江苏省,浦东新区,虹口区,金山区,长宁区,闵行区,青浦区,静安区,黄浦区</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -746,11 +745,11 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.8226322839432696</v>
+        <v>0.7971085731427003</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量`, `诉求区域` FROM `shanghai_ad_time` WHERE `新三级分类` LIKE '%擅自改变房屋使用性质%' AND `诉求区域` = '其他' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `事件数量`, GROUP_CONCAT(DISTINCT `诉求区域`) AS `涉及区域` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新四级分类` = '损坏房屋承重结构' AND `诉求区域` IN ('闵行区', '本市', '浦东新区', '宝山区', '奉贤区', '嘉定区', '松江区', '徐汇区', '杨浦区', '普陀区', '崇明区', '黄浦区', '长宁区', '虹口区', '静安区', '金山区', '青浦区', '江苏省', '浙江省', '其他', '安徽省');</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -793,11 +792,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9373866508847226</v>
+        <v>0.8705045276668262</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量`, `诉求区域` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND (`新三级分类` = '电力服务' OR `新三级分类` = '物业收费') AND `内容描述` LIKE '%飞线充电%' AND `内容描述` LIKE '%电动车上楼%' GROUP BY `诉求区域` LIMIT 10;</t>
+          <t>SELECT COUNT(*) AS `事件数量`, `诉求区域` AS `涉及地点` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND (`新三级分类` = '电力服务' OR `新三级分类` = '物业收费,停车管理') AND `诉求区域` NOT IN ('闵行区', '本市', '浦东新区', '宝山区', '奉贤区', '嘉定区', '松江区', '徐汇区', '杨浦区', '普陀区', '崇明区', '黄浦区', '长宁区', '虹口区', '静安区', '金山区', '青浦区', '江苏省', '浙江省', '其他', '安徽省') GROUP BY `诉求区域` LIMIT 10;</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -995,11 +994,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9149219928596286</v>
+        <v>0.8979854541342069</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `新三级分类` = '物业维修';</t>
+          <t>SELECT COUNT(*) AS `事件数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `新三级分类` IN ('物业收费', '物业维修');</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1275,11 +1274,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.802789480202639</v>
+        <v>0.821782014848853</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `新二级分类` = '公共体育设施' AND `工单类型` = '投诉举报类' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '公共体育设施' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1310,11 +1309,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9448098296602079</v>
+        <v>0.8733841541219197</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `客户类型` = '企业' AND `服务类型` = '企业服务' AND `工单生成时间` BETWEEN DATE_FORMAT(CURDATE(), '%Y-01-01') AND DATE_FORMAT(CURDATE(), '%Y-06-30');</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN '2023-01-01' AND '2023-06-30' AND `新三级分类` = '企业服务' AND `工单类型` IN ('求助类', '投诉举报类', '其他类', '意见建议类', '咨询类');</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1352,25 +1351,20 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.8891418753266143</v>
+        <v>0.8869045932324249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WITH order_counts AS (
-    SELECT `工单类型`, COUNT(*) AS `数量`
+          <t>WITH 工单类型统计 AS (
+    SELECT `工单类型`, COUNT(*) AS 数量
     FROM `shanghai_ad_time`
-    WHERE `新三级分类` = '企业服务'
-      AND `工单生成时间` BETWEEN DATE_FORMAT(CURDATE(), '%Y-01-01') AND DATE_FORMAT(CURDATE(), '%Y-06-30')
+    WHERE `工单生成时间` BETWEEN DATE_FORMAT(CURDATE(), '%Y-01-01') AND DATE_FORMAT(CURDATE(), '%Y-06-30')
+      AND `新三级分类` = '企业服务'
     GROUP BY `工单类型`
-), total_count AS (
-    SELECT COUNT(*) AS `总数`
-    FROM `shanghai_ad_time`
-    WHERE `新三级分类` = '企业服务'
-      AND `工单生成时间` BETWEEN DATE_FORMAT(CURDATE(), '%Y-01-01') AND DATE_FORMAT(CURDATE(), '%Y-06-30')
 )
-SELECT oc.`工单类型`, oc.`数量`, (oc.`数量` / tc.`总数`) * 100 AS `占比`
-FROM order_counts oc, total_count tc
-ORDER BY oc.`数量` DESC
+SELECT `工单类型`, 数量, (数量 / SUM(数量) OVER ()) * 100 AS 占比
+FROM 工单类型统计
+ORDER BY 数量 DESC
 LIMIT 10;</t>
         </is>
       </c>
@@ -1533,7 +1527,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1542,11 +1536,11 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9169641193768447</v>
+        <v>0.90965762496318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新二级分类` = '人力资源和社会保障' AND `工单类型` = '咨询类' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `社保业务咨询事件数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新三级分类` = '社保费与非税收入' AND `工单类型` = '咨询类';</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1568,7 +1562,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1577,11 +1571,11 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9038109905249333</v>
+        <v>0.9117326780671711</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新二级分类` = '税务' AND `工单类型` = '求助类' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `工单数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '税务' AND `工单类型` IN ('求助类', '投诉举报类', '其他类', '意见建议类', '咨询类');</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1612,11 +1606,11 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.968815303707612</v>
+        <v>0.9679763634828906</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `新四级分类` = '违法建筑' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单类型` = '投诉举报类' AND `新四级分类` = '违法建筑';</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1682,11 +1676,11 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.8930312017540702</v>
+        <v>0.9131194350659537</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `台风事件数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH);</t>
+          <t>SELECT COUNT(*) AS `台风事件数量` FROM `shanghai_ad_time` WHERE `新三级分类` LIKE '%台风沙尘%' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH);</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1703,25 +1697,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CORRECT</t>
+          <t>INCORRECT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>2347</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="E31" t="n">
-        <v>0.9563843805469788</v>
+        <v>0.8791214411260053</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-01-01') AND `工单生成时间` &lt; DATE_FORMAT(CURDATE() + INTERVAL 1 YEAR, '%Y-01-01') AND `工单类型` = '投诉举报类' AND `内容描述` LIKE '%加装电梯%';</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-01-01') AND `工单生成时间` &lt; DATE_FORMAT(CURDATE() + INTERVAL 1 YEAR, '%Y-01-01') AND `新二级分类` = '住房保障' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1743,7 +1737,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1752,11 +1746,11 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9686286697251758</v>
+        <v>0.8623189319726513</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 YEAR) AND `工单类型` = '咨询类' AND `内容描述` LIKE '%加装电梯%';</t>
+          <t>SELECT COUNT(*) AS `咨询工单数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 YEAR) AND `新二级分类` = '住房保障' AND `工单类型` = '咨询类';</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1776,7 +1770,15 @@
           <t>INCORRECT</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>求助类 517
+投诉举报类 411
+咨询类 151
+意见建议类 27
+其他类 3</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>求助类 105
@@ -1787,25 +1789,23 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.8402609874966579</v>
+        <v>0.829750018341733</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>WITH elevator_work_orders AS (
     SELECT `工单类型`, COUNT(*) AS `数量`
     FROM `shanghai_ad_time`
-    WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01')
+    WHERE `新二级分类` = '住房保障'
+      AND `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01')
       AND `工单生成时间` &lt;= LAST_DAY(CURDATE())
-      AND `新三级分类` = '旧住房改造'
-      AND `工单类型` = '求助类'
     GROUP BY `工单类型`
 ), total_count AS (
     SELECT COUNT(*) AS `总数`
     FROM `shanghai_ad_time`
-    WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01')
+    WHERE `新二级分类` = '住房保障'
+      AND `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01')
       AND `工单生成时间` &lt;= LAST_DAY(CURDATE())
-      AND `新三级分类` = '旧住房改造'
-      AND `工单类型` = '求助类'
 )
 SELECT e.`工单类型`, e.`数量`, (e.`数量` / t.`总数`) * 100 AS `占比`
 FROM elevator_work_orders e, total_count t
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9313127478474098</v>
+        <v>0.9263069251897783</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `新三级分类` = '排水设施' AND `工单类型` = '求助类';</t>
+          <t>SELECT COUNT(*) AS `求助工单数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `新三级分类` IN ('排水设施', '市政道路积水') AND `工单类型` = '求助类';</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1876,11 +1876,11 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9068989583396588</v>
+        <v>0.8895362410220373</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `三级分类` = '房屋维修添置';</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `三级分类` = '物业维修';</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1911,11 +1911,11 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.8758075679208297</v>
+        <v>0.8577413540795512</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `工单类型` = '求助类';</t>
+          <t>SELECT COUNT(*) AS `与台风相关的求助类工单数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `工单类型` = '求助类';</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1946,11 +1946,11 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.8354863842903086</v>
+        <v>0.8168456465467533</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `新二级分类` = '绿化';</t>
+          <t>SELECT COUNT(*) AS `树木倒伏事件数量` FROM `shanghai_ad_time` WHERE (`新三级分类` = '台风沙尘' OR `新三级分类` = '绿化维护,消防隐患') AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1989,11 +1989,11 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.7822919898774781</v>
+        <v>0.8114819867962175</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SELECT DISTINCT `诉求区域`, `诉求地址` FROM shanghai_ad_time WHERE `新三级分类` = '农业' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT DISTINCT `诉求区域` FROM `shanghai_ad_time` WHERE `工单类型` = '投诉举报类' AND `新三级分类` = '农业灾害';</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2024,11 +2024,11 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9004552102023611</v>
+        <v>0.8963649713082311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单类型` = '投诉举报类' AND `新二级分类` = '教育' AND `一级分类` = '科教文卫类';</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `一级分类` = '科教文卫类' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2059,11 +2059,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.8874125404578206</v>
+        <v>0.8732794905938773</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `事件数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `四级分类` = '市政道路积水' AND `新二级分类` = '人口管理';</t>
+          <t>SELECT COUNT(*) AS `事件数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '台风沙尘' AND `四级分类` = '市政道路积水' AND `新二级分类` != '居民生活服务' AND `新二级分类` != '社会管理';</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2094,11 +2094,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9250951932313858</v>
+        <v>0.9316708037604461</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `四级分类` = '业委会' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `四级分类` LIKE '%业委会%';</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>237</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2129,11 +2129,11 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9504996862977712</v>
+        <v>0.9199935235065487</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01') AND `工单生成时间` &lt;= LAST_DAY(CURDATE()) AND `四级分类` = '审验登记' AND `工单类型` = '咨询类';</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01') AND `工单生成时间` &lt;= LAST_DAY(CURDATE()) AND `四级分类` = '审验登记' AND `服务类型` = '一网通办';</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2164,11 +2164,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9523468515203015</v>
+        <v>0.9435859990216244</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01') AND `工单生成时间` &lt;= LAST_DAY(CURDATE()) AND `四级分类` = '入学政策' AND `工单类型` = '咨询类';</t>
+          <t>SELECT COUNT(*) AS `工单数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= DATE_FORMAT(CURDATE(), '%Y-%m-01') AND `工单生成时间` &lt;= LAST_DAY(CURDATE()) AND `四级分类` = '入学政策';</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2255,25 +2255,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CORRECT</t>
+          <t>INCORRECT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="E46" t="n">
-        <v>0.9663893667985692</v>
+        <v>0.9141661646174493</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉事件数量` FROM `shanghai_ad_time` WHERE `四级分类` = '医保报销' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉事件数量` FROM `shanghai_ad_time` WHERE `工单类别` LIKE '%医保报销%' AND `内容描述` LIKE '%投诉%';</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2296,15 +2296,15 @@
       <c r="C47" t="inlineStr">
         <is>
           <t>None
-None
-None
-None
-None
-None
 市住房城乡建设管理委
-None
-None
-None</t>
+杨浦区人民政府
+奉贤区人民政府
+闵行区人民政府
+松江区人民政府
+宝山区人民政府
+徐汇区人民政府
+嘉定区人民政府
+静安区人民政府</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2322,11 +2322,11 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9042939187820362</v>
+        <v>0.8920728003788578</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SELECT `主办单位` FROM `shanghai_ad_time` WHERE `内容描述` LIKE '%拖欠工资%' LIMIT 10;</t>
+          <t>SELECT DISTINCT `主办单位` FROM `shanghai_ad_time` WHERE `内容描述` LIKE '%拖欠工资%' LIMIT 10;</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2357,11 +2357,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9371156205955884</v>
+        <v>0.9037192672746792</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `新二级分类` = '表扬感谢';</t>
+          <t>SELECT COUNT(*) AS `表扬工单数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `新二级分类` = '表扬感谢' AND `工单类型` IN ('求助类', '投诉举报类', '其他类', '意见建议类', '咨询类');</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2444,30 +2444,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>None
-嘉定区人民政府
-供水热线
-浦东新区人民政府
-普陀区人民政府
-杨浦区人民政府
-金山区人民政府
-闵行区人民政府
-长兴岛开发建设管理委员会
-静安区人民政府
-市水务局
-长宁区人民政府
-松江区人民政府
-中国联通上海公司
-上海铁路局
-宝山区人民政府
-燃气热线
-青浦区人民政府
-市卫生健康委
-市房屋管理局
-徐汇区人民政府
-奉贤区人民政府
-崇明区人民政府
-虹口区人民政府</t>
+          <t>浦东新区人民政府 12
+None 4
+奉贤区人民政府 2
+金山区人民政府 1
+杨浦区人民政府 1
+长宁区人民政府 1
+松江区人民政府 1
+嘉定区人民政府 1
+市交通委 1
+静安区人民政府 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2485,11 +2471,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.954564552895226</v>
+        <v>0.9085093322860884</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SELECT DISTINCT `主办单位` FROM shanghai_ad_time WHERE `四级分类` = '市政道路积水';</t>
+          <t>SELECT `主办单位`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `内容描述` LIKE '%道路积水%' GROUP BY `主办单位` ORDER BY `数量` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2546,7 +2532,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>其他类 54</t>
+          <t>求助类 104225
+投诉举报类 42219
+其他类 12388
+意见建议类 4136
+咨询类 58061</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2559,34 +2549,36 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9059440629190235</v>
+        <v>0.8233608166902651</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WITH categorized_orders AS (
+          <t>WITH 工单分类 AS (
     SELECT
-        CASE
-            WHEN `工单类型` = '诉求类' THEN '诉求类'
-            WHEN `工单类型` = '投诉类' THEN '投诉类'
-            WHEN `工单类型` = '咨询类' THEN '咨询类'
-            WHEN `工单类型` = '建议类' THEN '建议类'
-            ELSE '其他类'
-        END AS order_type,
-        COUNT(*) AS order_count
+        `工单类型`,
+        COUNT(*) AS `数量`
     FROM
-        shanghai_ad_time
+        `shanghai_ad_time`
     WHERE
-        `新四级分类` = '违法建筑'
-        AND `工单类型` = '求助类'
+        `工单类型` IN ('求助类', '投诉举报类', '其他类', '意见建议类', '咨询类')
     GROUP BY
-        order_type
+        `工单类型`
+),
+总工单数量 AS (
+    SELECT
+        COUNT(*) AS `总数`
+    FROM
+        `shanghai_ad_time`
+    WHERE
+        `工单类型` IN ('求助类', '投诉举报类', '其他类', '意见建议类', '咨询类')
 )
 SELECT
-    order_type,
-    order_count,
-    (order_count * 100.0 / SUM(order_count) OVER ()) AS percentage
+    `工单类型`,
+    `数量`,
+    (`数量` / `总数`) * 100 AS `占比`
 FROM
-    categorized_orders;</t>
+    工单分类,
+    总工单数量;</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2606,13 +2598,7 @@
           <t>INCORRECT</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>投诉 121
-咨询 8
-诉求 7</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>投诉举报类 121
@@ -2621,11 +2607,11 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.9080250698435248</v>
+        <v>0.8871441256642387</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WITH categorized_workorders AS (
+          <t>WITH categorized_counts AS (
     SELECT
         CASE
             WHEN `工单类型` = '求助类' THEN '诉求'
@@ -2633,21 +2619,30 @@
             WHEN `工单类型` = '咨询类' THEN '咨询'
             WHEN `新四级分类` = '意见建议' THEN '建议'
             ELSE '其他'
-        END AS category,
-        COUNT(*) AS count
+        END AS 类型,
+        COUNT(*) AS 数量
     FROM
-        shanghai_ad_time
+        `shanghai_ad_time`
     WHERE
-        `四级分类` = '居改非'
+        `新二级分类` = '居改非'
     GROUP BY
-        category
+        类型
+),
+ total_count AS (
+    SELECT
+        SUM(数量) AS 总数量
+    FROM
+        categorized_counts
 )
 SELECT
-    category,
-    count,
-    (count * 100.0 / SUM(count) OVER ()) AS percentage
+    c.类型,
+    c.数量,
+    (c.数量 / t.总数量) * 100 AS 比例
 FROM
-    categorized_workorders;</t>
+    categorized_counts c,
+    total_count t
+ORDER BY
+    比例 DESC;</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2669,16 +2664,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>静安区 7
-徐汇区 11
-青浦区 6
-金山区 1
-普陀区 9
-黄浦区 4
-浦东新区 20
-宝山区 22
-闵行区 10
-崇明区 4</t>
+          <t>静安区
+徐汇区
+青浦区
+金山区
+普陀区
+黄浦区
+浦东新区
+宝山区
+闵行区
+崇明区
+嘉定区
+本市
+长宁区
+奉贤区
+虹口区
+杨浦区
+松江区
+江苏省</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2696,11 +2699,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9144472673470889</v>
+        <v>0.869130235142173</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SELECT `诉求区域`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新四级分类` = '损坏房屋承重结构' GROUP BY `诉求区域` LIMIT 10;</t>
+          <t>SELECT DISTINCT `诉求区域` FROM `shanghai_ad_time` WHERE `新四级分类` = '损坏房屋承重结构' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2736,11 +2739,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.9435181377792885</v>
+        <v>0.9268840964691459</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SELECT DISTINCT `诉求区域` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `诉求区域` = '其他' AND `新二级分类` = '动迁政策';</t>
+          <t>SELECT `诉求区域` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `诉求区域` IN ('闵行区', '本市', '浦东新区', '宝山区', '奉贤区', '嘉定区', '松江区', '徐汇区', '杨浦区', '普陀区', '崇明区', '黄浦区', '长宁区', '虹口区', '静安区', '金山区', '青浦区', '江苏省', '浙江省', '其他', '安徽省') AND `客户类型` = '个人' AND `新三级分类` = '动迁政策' LIMIT 10;</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2771,11 +2774,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8711441641596376</v>
+        <v>0.8789155483158897</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉量` FROM `shanghai_ad_time` WHERE `新一级分类` = '住房和城乡建设类' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉量` FROM `shanghai_ad_time` WHERE `工单类型` = '投诉举报类' AND `新一级分类` = '住房和城乡建设类';</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2797,7 +2800,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>None 445</t>
+          <t>None 318</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2815,11 +2818,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9807394428395448</v>
+        <v>0.978204959323862</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SELECT `主办单位`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `四级分类` = '服务态度' GROUP BY `主办单位` ORDER BY `数量` DESC LIMIT 1;</t>
+          <t>SELECT `主办单位`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新四级分类` = '服务态度' GROUP BY `主办单位` ORDER BY `数量` DESC LIMIT 1;</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2925,11 +2928,11 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9350114980383286</v>
+        <v>0.8937186534244034</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SELECT `诉求区域`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '垃圾清理' AND `工单类型` = '投诉举报类' AND `诉求区域` = '其他' GROUP BY `诉求区域` ORDER BY `数量` DESC LIMIT 10;</t>
+          <t>SELECT `诉求区域`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '垃圾清理' AND `工单类型` = '投诉举报类' AND `诉求区域` IN ('闵行区', '本市', '浦东新区', '宝山区', '奉贤区', '嘉定区', '松江区', '徐汇区', '杨浦区', '普陀区', '崇明区', '黄浦区', '长宁区', '虹口区', '静安区', '金山区', '青浦区') GROUP BY `诉求区域` ORDER BY `数量` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2946,11 +2949,10 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>INCORRECT</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>浦东新区 50
 闵行区 19
@@ -2964,12 +2966,26 @@
 青浦区 11</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>浦东新区 50
+闵行区 19
+普陀区 17
+宝山区 16
+松江区 16
+杨浦区 15
+静安区 13
+长宁区 13
+奉贤区 13
+青浦区 11</t>
+        </is>
+      </c>
       <c r="E61" t="n">
-        <v>0.9777248746595287</v>
+        <v>0.9363616069410547</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SELECT `诉求区域`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `诉求区域` = '其他' AND `四级分类` = '油烟扰民' GROUP BY `诉求区域` ORDER BY `数量` DESC LIMIT 10;</t>
+          <t>SELECT `诉求区域`, COUNT(*) AS `油烟扰民事件数量` FROM `shanghai_ad_time` WHERE `四级分类` = '油烟扰民' AND `诉求区域` IN ('闵行区', '本市', '浦东新区', '宝山区', '奉贤区', '嘉定区', '松江区', '徐汇区', '杨浦区', '普陀区', '崇明区', '黄浦区', '长宁区', '虹口区', '静安区', '金山区', '青浦区', '江苏省', '浙江省', '其他', '安徽省') GROUP BY `诉求区域` ORDER BY `油烟扰民事件数量` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3024,20 +3040,7 @@
           <t>INCORRECT</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>本市 22902
-浦东新区 7156
-闵行区 3015
-宝山区 2182
-长宁区 2180
-杨浦区 2071
-嘉定区 1950
-松江区 1793
-徐汇区 1793
-静安区 1619</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>投诉举报类 61
@@ -3047,25 +3050,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8653720817986994</v>
+        <v>0.8371737137235964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WITH complaint_counts AS (
-    SELECT `诉求区域`, COUNT(*) AS `complaint_count`
-    FROM shanghai_ad_time
-    WHERE `工单类型` IN ('投诉举报类', '其他类')
-    GROUP BY `诉求区域`
+          <t>WITH 工单分类 AS (
+    SELECT `新三级分类`, COUNT(*) AS `数量`
+    FROM `shanghai_ad_time`
+    WHERE `新三级分类` = '推诿扯皮'
+    GROUP BY `新三级分类`
 ),
- total_complaints AS (
-    SELECT COUNT(*) AS `total_count`
-    FROM shanghai_ad_time
-    WHERE `工单类型` IN ('投诉举报类', '其他类')
+总工单数量 AS (
+    SELECT COUNT(*) AS `总数`
+    FROM `shanghai_ad_time`
+    WHERE `新三级分类` = '推诿扯皮'
 )
-SELECT cc.`诉求区域`, cc.`complaint_count`, (cc.`complaint_count` / tc.`total_count`) * 100 AS `percentage`
-FROM complaint_counts cc, total_complaints tc
-ORDER BY `percentage` DESC
-LIMIT 10;</t>
+SELECT `新三级分类`, (`数量` / `总数`) * 100 AS `比例`
+FROM 工单分类, 总工单数量;</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3085,7 +3086,14 @@
           <t>INCORRECT</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>求助类 99
+投诉举报类 87
+咨询类 12
+意见建议类 8</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>求助类 99
@@ -3096,28 +3104,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8421051955482598</v>
+        <v>0.8661500884836059</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WITH categorized_orders AS (
+          <t>WITH 工单分类 AS (
     SELECT
-        `工单类型`,
-        COUNT(*) AS `数量`
+        CASE
+            WHEN `工单类型` = '求助类' THEN '求助类'
+            WHEN `工单类型` = '投诉举报类' THEN '投诉举报类'
+            WHEN `工单类型` = '意见建议类' THEN '意见建议类'
+            WHEN `工单类型` = '咨询类' THEN '咨询类'
+        END AS 类型,
+        COUNT(*) AS 数量
     FROM
         `shanghai_ad_time`
     WHERE
-        `新二级分类` = '交通管理'
-        AND `工单类型` IN ('求助类', '投诉', '咨询', '建议')
+        `内容描述` LIKE '%电瓶车充电%'
+        AND `工单类型` IN ('求助类', '投诉举报类', '意见建议类', '咨询类')
     GROUP BY
-        `工单类型`
+        类型
+), 总计 AS (
+    SELECT
+        SUM(数量) AS 总数量
+    FROM
+        工单分类
 )
 SELECT
-    `工单类型`,
-    `数量`,
-    (`数量` / SUM(`数量`) OVER ()) * 100 AS `占比`
+    类型,
+    数量,
+    (数量 / 总数量) * 100 AS 百分比
 FROM
-    categorized_orders;</t>
+    工单分类,
+    总计
+ORDER BY
+    百分比 DESC
+LIMIT 10;</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3139,7 +3161,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3148,11 +3170,11 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8971989801763106</v>
+        <v>0.9064599107647813</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `新四级分类` = '电信诈骗' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `投诉被诈骗工单数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新四级分类` = '电信诈骗' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3183,11 +3205,11 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8875667878389591</v>
+        <v>0.8591105892199286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '残疾人福利';</t>
+          <t>SELECT COUNT(*) AS `事件数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` LIKE '%残疾人福利%';</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3204,12 +3226,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>INCORRECT</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3218,11 +3240,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8522798346048504</v>
+        <v>0.964767656115419</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND CURDATE() AND `新三级分类` = '就业创业';</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND CURDATE() AND `工单类型` = '投诉举报类' AND `内容描述` LIKE '%咸鱼平台%';</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3244,7 +3266,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3253,11 +3275,11 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9400482822916658</v>
+        <v>0.9422228122828138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `一级分类` = '科教文卫类';</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新一级分类` = '教育';</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3279,7 +3301,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3288,11 +3310,11 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9263067874236891</v>
+        <v>0.9414592970854071</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `三级分类` = '医院监管' AND YEAR(`工单生成时间`) = YEAR(CURDATE());</t>
+          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND (`三级分类` = '医院医疗信息' OR `三级分类` = '医疗服务');</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3349,7 +3371,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3358,11 +3380,11 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.936935608978284</v>
+        <v>0.9354445831918154</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新三级分类` = '人事人才' AND `工单类型` = '咨询类' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 2 MONTH);</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 2 MONTH) AND `新二级分类` = '人事人才' AND `工单类型` = '咨询类';</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3384,7 +3406,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>166000</t>
+          <t>32171</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3393,11 +3415,11 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9283596397786538</v>
+        <v>0.9371668957021236</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `服务类型` = '综合服务';</t>
+          <t>SELECT COUNT(*) AS `投诉工单数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `服务类型` = '综合服务' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3414,25 +3436,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CORRECT</t>
+          <t>INCORRECT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
           <t>780</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>780</t>
-        </is>
-      </c>
       <c r="E73" t="n">
-        <v>0.9861607188796389</v>
+        <v>0.9076861768041544</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `内容描述` LIKE '%拖欠工资%' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH);</t>
+          <t>SELECT COUNT(*) AS `拖欠工资事件数量` FROM `shanghai_ad_time` WHERE `新四级分类` = '拖欠工资' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH);</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3489,7 +3511,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>520</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3498,11 +3520,11 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.892427670074128</v>
+        <v>0.8974364286976395</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `新二级分类` = '医疗保险' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH);</t>
+          <t>SELECT COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `新三级分类` IN ('医保待遇', '医疗保险');</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3533,11 +3555,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9119822755466229</v>
+        <v>0.9109398900940507</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '金融' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉事件数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` LIKE '%金融%' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3568,11 +3590,11 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9125884437126106</v>
+        <v>0.9037890658647563</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SELECT COUNT(*) AS `投诉数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '金融' AND `工单类型` = '投诉举报类';</t>
+          <t>SELECT COUNT(*) AS `投诉事件数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新二级分类` = '金融' AND `工单类型` = '投诉举报类';</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3589,29 +3611,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CORRECT</t>
+          <t>INCORRECT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
+        <is>
+          <t>投诉举报类 1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>咨询类 189
 求助类 68
 投诉举报类 1</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>咨询类 189
-求助类 68
-投诉举报类 1</t>
-        </is>
-      </c>
       <c r="E78" t="n">
-        <v>0.9732629898804546</v>
+        <v>0.9661281187589262</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SELECT `工单类型`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` &gt;= '2024-01-01' AND `工单生成时间` &lt; '2025-01-01' AND `四级分类` = '医保政策咨询' GROUP BY `工单类型` ORDER BY `数量` DESC LIMIT 10;</t>
+          <t>SELECT `工单类型`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = 2024 AND `四级分类` LIKE '%医保政策咨询%' AND `工单类型` LIKE '%投诉举报类%' GROUP BY `工单类型` ORDER BY `数量` DESC LIMIT 10;</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3739,11 +3759,11 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.9571251035607939</v>
+        <v>0.9675287775651527</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>SELECT DATE_FORMAT(`工单生成时间`, '%Y-%m') AS `月份`, COUNT(*) AS `离婚办理数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = 2024 AND `四级分类` = '离婚办理' GROUP BY `月份` ORDER BY `月份`;</t>
+          <t xml:space="preserve">SELECT DATE_FORMAT(`工单生成时间`, '%Y-%m') AS `月份`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE YEAR(`工单生成时间`) = 2024 AND `四级分类` = '离婚办理' GROUP BY `月份` ORDER BY `月份`; </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3766,11 +3786,11 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>0.9735728531807286</v>
+        <v>0.9590665553566815</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SELECT DATE_FORMAT(`工单生成时间`, '%Y-%u') AS `周`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN '2024-05-01' AND '2024-05-31' AND `诉求区域` = '浦东新区' AND `四级分类` = '交通违章' GROUP BY DATE_FORMAT(`工单生成时间`, '%Y-%u') ORDER BY `周`;</t>
+          <t xml:space="preserve">SELECT DATE_FORMAT(`工单生成时间`, '%Y-%u') AS `周数`, COUNT(*) AS `数量` FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN '2024-05-01' AND '2024-05-31' AND `诉求区域` LIKE '%浦东新区%' AND `四级分类` LIKE '%交通违章%' GROUP BY DATE_FORMAT(`工单生成时间`, '%Y-%u') ORDER BY `周数`; </t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3801,11 +3821,11 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.8878623792134883</v>
+        <v>0.9074905923555016</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SELECT (SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单生成时间` BETWEEN '2024-06-01' AND '2024-06-30') - (SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单生成时间` BETWEEN '2024-05-01' AND '2024-05-31') AS `数量差值`;</t>
+          <t>SELECT (SELECT COUNT(*) FROM `shanghai_ad_time` WHERE DATE(`工单生成时间`) BETWEEN '2024-06-01' AND '2024-06-30') - (SELECT COUNT(*) FROM `shanghai_ad_time` WHERE DATE(`工单生成时间`) BETWEEN '2024-05-01' AND '2024-05-31') AS `差值`;</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3836,11 +3856,11 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.956248243656673</v>
+        <v>0.9385827368627879</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SELECT (SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单生成时间` BETWEEN '2024-06-01' AND '2024-06-30' AND `诉求区域` = '浦东新区' AND `工单类型` = '投诉举报类') - (SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单生成时间` BETWEEN '2024-06-01' AND '2024-06-30' AND `诉求区域` = '虹口区' AND `工单类型` = '投诉举报类') AS `差值`;</t>
+          <t>SELECT (SELECT COUNT(*) FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN '2024-06-01' AND '2024-06-30' AND `诉求区域` = '浦东新区' AND `工单类型` = '投诉举报类') - (SELECT COUNT(*) FROM `shanghai_ad_time` WHERE `工单生成时间` BETWEEN '2024-06-01' AND '2024-06-30' AND `诉求区域` = '虹口区' AND `工单类型` = '投诉举报类') AS `投诉工单量差值`;</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3857,12 +3877,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>INCORRECT</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3871,11 +3891,24 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9462580425601276</v>
+        <v>0.9650316676981839</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SELECT (`社会管理类` - `公安政法类`) AS `数量差` FROM ( SELECT SUM(CASE WHEN `一级分类` = '社会管理类' THEN 1 ELSE 0 END) AS `社会管理类`, SUM(CASE WHEN `一级分类` = '公安政法类' THEN 1 ELSE 0 END) AS `公安政法类` FROM shanghai_ad_time WHERE `工单生成时间` BETWEEN '2024-01-01' AND '2024-01-31' ) AS subquery;</t>
+          <t>WITH 社会管理类工单 AS (
+    SELECT COUNT(*) AS 社会管理类数量
+    FROM `shanghai_ad_time`
+    WHERE `工单生成时间` BETWEEN '2024-01-01' AND '2024-01-31'
+      AND `一级分类` = '社会管理类'
+),
+公安政法类工单 AS (
+    SELECT COUNT(*) AS 公安政法类数量
+    FROM `shanghai_ad_time`
+    WHERE `工单生成时间` BETWEEN '2024-01-01' AND '2024-01-31'
+      AND `一级分类` = '公安政法类'
+)
+SELECT (社会管理类数量 - 公安政法类数量) AS 数量差
+FROM 社会管理类工单, 公安政法类工单;</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3887,17 +3920,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>总耗时: 16.3</t>
+          <t>总耗时: 17.7</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>关键点抽取: 4.18</t>
+          <t>关键点抽取: 4.33</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>时间掩码: 0.59</t>
+          <t>时间掩码: 0.58</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3907,12 +3940,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>元数据关联: 7.92</t>
+          <t>元数据关联: 8.58</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>生成: 2.29</t>
+          <t>生成: 2.61</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>错误重写: 0.28</t>
         </is>
       </c>
     </row>
